--- a/artfynd/A 12191-2026 artfynd.xlsx
+++ b/artfynd/A 12191-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132805756</v>
       </c>
       <c r="B2" t="n">
-        <v>92564</v>
+        <v>92565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>132805723</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>132805610</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12191-2026 artfynd.xlsx
+++ b/artfynd/A 12191-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132805756</v>
       </c>
       <c r="B2" t="n">
-        <v>92565</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12191-2026 artfynd.xlsx
+++ b/artfynd/A 12191-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132805756</v>
       </c>
       <c r="B2" t="n">
-        <v>92567</v>
+        <v>92568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
